--- a/Pruebas calificadas/COLEGIO-BELLAVISTA-(IED)-PRUEBA-DIAGNÓSTICA-1103_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-BELLAVISTA-(IED)-PRUEBA-DIAGNÓSTICA-1103_CALIFICADO.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ68"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17697,6 +17697,179 @@
         <v/>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>111001098892</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO BELLAVISTA (IED)</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>SAMY YULIANA HERNANDEZ BAUTISTA</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>1141327491</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>1103</v>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr"/>
+      <c r="P69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr"/>
+      <c r="X69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr"/>
+      <c r="Z69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr"/>
+      <c r="AB69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE69" s="2" t="inlineStr"/>
+      <c r="AF69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG69" s="2" t="inlineStr"/>
+      <c r="AH69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI69" s="2" t="inlineStr"/>
+      <c r="AJ69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK69" s="2" t="inlineStr"/>
+      <c r="AL69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM69" s="2" t="inlineStr"/>
+      <c r="AN69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO69" s="2" t="inlineStr"/>
+      <c r="AP69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ69" s="2" t="inlineStr"/>
+      <c r="AR69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS69" s="2" t="inlineStr"/>
+      <c r="AT69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU69" s="2" t="inlineStr"/>
+      <c r="AV69" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW69" s="5">
+        <f>COUNTIF(J69:AV69,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX69" s="5">
+        <f>COUNTIF(J69:AV69,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY69" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ69" s="6">
+        <f>AW69/AY69</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pruebas calificadas/COLEGIO-BELLAVISTA-(IED)-PRUEBA-DIAGNÓSTICA-1103_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-BELLAVISTA-(IED)-PRUEBA-DIAGNÓSTICA-1103_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -2337,7 +2309,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -2590,7 +2558,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -2843,7 +2807,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3084,11 +3048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -3096,7 +3056,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3337,11 +3297,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -3349,7 +3305,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3590,11 +3546,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -3602,7 +3554,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3843,11 +3795,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -3855,7 +3803,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4096,11 +4044,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -4108,7 +4052,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4349,11 +4293,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -4361,7 +4301,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4602,11 +4542,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -4614,7 +4550,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4855,11 +4791,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -4867,7 +4799,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5108,11 +5040,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -5120,7 +5048,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5361,11 +5289,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -5373,7 +5297,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5614,11 +5538,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -5626,7 +5546,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5867,11 +5787,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -5879,7 +5795,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6116,11 +6032,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -6128,7 +6040,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6369,11 +6281,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -6381,7 +6289,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6622,11 +6530,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -6634,7 +6538,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6875,11 +6779,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -6887,7 +6787,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7128,11 +7028,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -7140,7 +7036,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7381,11 +7277,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -7393,7 +7285,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7634,11 +7526,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -7646,7 +7534,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7887,11 +7775,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -7899,7 +7783,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8140,11 +8024,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -8152,7 +8032,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8393,11 +8273,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -8405,7 +8281,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8598,11 +8474,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -8610,7 +8482,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8851,11 +8723,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -8863,7 +8731,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9104,11 +8972,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -9116,7 +8980,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9353,11 +9217,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -9365,7 +9225,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9606,11 +9466,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -9618,7 +9474,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9859,11 +9715,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -9871,7 +9723,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10112,11 +9964,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -10124,7 +9972,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10365,11 +10213,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -10377,7 +10221,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10618,11 +10462,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -10630,7 +10470,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10871,11 +10711,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -10883,7 +10719,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11124,11 +10960,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -11136,7 +10968,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11377,11 +11209,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -11389,7 +11217,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11630,11 +11458,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -11642,7 +11466,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11883,11 +11707,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -11895,7 +11715,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12136,11 +11956,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -12148,7 +11964,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12389,11 +12205,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -12401,7 +12213,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12642,11 +12454,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -12654,7 +12462,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12895,11 +12703,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -12907,7 +12711,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13144,11 +12948,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -13156,7 +12956,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13397,11 +13197,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -13409,7 +13205,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13650,11 +13446,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -13662,7 +13454,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13903,11 +13695,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -13915,7 +13703,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14156,11 +13944,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -14168,7 +13952,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14409,11 +14193,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -14421,7 +14201,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14662,11 +14442,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -14674,7 +14450,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14915,11 +14691,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -14927,7 +14699,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15168,11 +14940,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -15180,7 +14948,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15421,11 +15189,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -15433,7 +15197,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15674,11 +15438,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -15686,7 +15446,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15927,11 +15687,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -15939,7 +15695,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16180,11 +15936,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -16192,7 +15944,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16433,11 +16185,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -16445,7 +16193,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16686,11 +16434,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -16698,7 +16442,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16939,11 +16683,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -16951,7 +16691,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17192,11 +16932,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -17204,7 +16940,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17445,11 +17181,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -17457,7 +17189,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17698,11 +17430,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -17710,7 +17438,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BELLAVISTA (IED)</t>
+          <t>COLEGIO BELLAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
